--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 03/NKSX_100TG102LE4G-ESIM(0056)_110326.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 03/NKSX_100TG102LE4G-ESIM(0056)_110326.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E647DF-50F4-4955-A298-31E1652FBE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA35C3B-E6E1-4701-83FF-FE41D866EA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="332">
   <si>
     <t>STT</t>
   </si>
@@ -1014,13 +1014,16 @@
     <t>1150021747</t>
   </si>
   <si>
-    <t>Thùng 1_IMEI</t>
-  </si>
-  <si>
-    <t>Thùng 2_ IMEI</t>
-  </si>
-  <si>
     <t>SERRI</t>
+  </si>
+  <si>
+    <t>Thùng 1</t>
+  </si>
+  <si>
+    <t>Thùng 2</t>
+  </si>
+  <si>
+    <t>IMEI</t>
   </si>
 </sst>
 </file>
@@ -1341,7 +1344,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1454,6 +1457,10 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1511,8 +1518,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1940,66 +1955,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="58"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="60"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="57" t="s">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="60"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="59" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="62"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -2250,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84643D1D-8ECE-4260-8771-C158F2DB8341}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="37" customWidth="1"/>
@@ -2259,1179 +2274,1197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="64" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" s="65"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="64" t="s">
+        <v>330</v>
+      </c>
+      <c r="F1" s="65"/>
+      <c r="G1" s="66"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="63"/>
+      <c r="B2" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="C2" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="C1" s="38" t="s">
-        <v>330</v>
-      </c>
-      <c r="D1" s="38" t="s">
+      <c r="D2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="39" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="G1" s="39" t="s">
+      <c r="E2" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>328</v>
+      </c>
+      <c r="G2" s="39" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="36">
-        <v>1</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="61" t="s">
-        <v>232</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>281</v>
-      </c>
-      <c r="G2" s="41" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>233</v>
+        <v>32</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>232</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="42" t="s">
         <v>281</v>
       </c>
       <c r="G3" s="41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>234</v>
+        <v>33</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>233</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="61" t="s">
-        <v>282</v>
+        <v>83</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>281</v>
       </c>
       <c r="G4" s="41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="61" t="s">
-        <v>235</v>
+        <v>34</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>234</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="61" t="s">
-        <v>283</v>
+        <v>84</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>282</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="61" t="s">
-        <v>236</v>
+        <v>35</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>235</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="61" t="s">
-        <v>284</v>
+        <v>85</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>283</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>237</v>
+        <v>36</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>236</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="61" t="s">
-        <v>285</v>
+        <v>86</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>284</v>
       </c>
       <c r="G7" s="41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>238</v>
+        <v>37</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>237</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="61" t="s">
-        <v>286</v>
+        <v>87</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>285</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>239</v>
+        <v>38</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>238</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E9" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" s="61" t="s">
-        <v>287</v>
+        <v>88</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>286</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>240</v>
+        <v>39</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>239</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="61" t="s">
-        <v>288</v>
+        <v>89</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>287</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>241</v>
+        <v>40</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>240</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="61" t="s">
-        <v>289</v>
+        <v>90</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>288</v>
       </c>
       <c r="G11" s="41" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>242</v>
+        <v>41</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>241</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>290</v>
+        <v>91</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>289</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="61" t="s">
-        <v>243</v>
+        <v>42</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>242</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" s="61" t="s">
-        <v>291</v>
+        <v>92</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>290</v>
       </c>
       <c r="G13" s="41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>244</v>
+        <v>43</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>243</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="61" t="s">
-        <v>292</v>
+        <v>93</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>291</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="61" t="s">
-        <v>245</v>
+        <v>44</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>244</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="61" t="s">
-        <v>293</v>
+        <v>94</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>292</v>
       </c>
       <c r="G15" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="61" t="s">
-        <v>246</v>
+        <v>45</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>245</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="61" t="s">
-        <v>294</v>
+        <v>95</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>293</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="61" t="s">
-        <v>247</v>
+        <v>46</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>246</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="61" t="s">
-        <v>295</v>
+        <v>96</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>294</v>
       </c>
       <c r="G17" s="41" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="61" t="s">
-        <v>248</v>
+        <v>47</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>247</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="61" t="s">
-        <v>296</v>
+        <v>97</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>295</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>249</v>
+        <v>48</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>248</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="61" t="s">
-        <v>297</v>
+        <v>98</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>296</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>250</v>
+        <v>49</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>249</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="61" t="s">
-        <v>298</v>
+        <v>99</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>297</v>
       </c>
       <c r="G20" s="41" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="61" t="s">
-        <v>251</v>
+        <v>50</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>250</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="61" t="s">
-        <v>299</v>
+        <v>100</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>298</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="61" t="s">
-        <v>252</v>
+        <v>51</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>251</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="61" t="s">
-        <v>300</v>
+        <v>101</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>299</v>
       </c>
       <c r="G22" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="61" t="s">
-        <v>253</v>
+        <v>52</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>252</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="61" t="s">
-        <v>301</v>
+        <v>102</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>300</v>
       </c>
       <c r="G23" s="41" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="61" t="s">
-        <v>254</v>
+        <v>53</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>253</v>
       </c>
       <c r="D24" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="61" t="s">
-        <v>302</v>
+        <v>103</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>301</v>
       </c>
       <c r="G24" s="41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="61" t="s">
-        <v>255</v>
+        <v>54</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>254</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" s="61" t="s">
-        <v>303</v>
+        <v>104</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>302</v>
       </c>
       <c r="G25" s="41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="61" t="s">
-        <v>256</v>
+        <v>55</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>255</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="61" t="s">
-        <v>304</v>
+        <v>105</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>303</v>
       </c>
       <c r="G26" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="61" t="s">
-        <v>257</v>
+        <v>56</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>256</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="61" t="s">
-        <v>305</v>
+        <v>106</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>304</v>
       </c>
       <c r="G27" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="61" t="s">
-        <v>258</v>
+        <v>57</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>257</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="61" t="s">
-        <v>306</v>
+        <v>107</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>305</v>
       </c>
       <c r="G28" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="61" t="s">
-        <v>259</v>
+        <v>58</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>258</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" s="61" t="s">
-        <v>307</v>
+        <v>108</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>306</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="61" t="s">
-        <v>260</v>
+        <v>59</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>259</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="F30" s="61" t="s">
-        <v>308</v>
+        <v>109</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>307</v>
       </c>
       <c r="G30" s="41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="61" t="s">
-        <v>261</v>
+        <v>60</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>260</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31" s="61" t="s">
-        <v>309</v>
+        <v>110</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>308</v>
       </c>
       <c r="G31" s="41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="36">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="61" t="s">
-        <v>262</v>
+        <v>61</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>261</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="F32" s="61" t="s">
-        <v>310</v>
+        <v>111</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>309</v>
       </c>
       <c r="G32" s="41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="36">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="61" t="s">
-        <v>263</v>
+        <v>62</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>262</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="61" t="s">
-        <v>311</v>
+        <v>112</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>310</v>
       </c>
       <c r="G33" s="41" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="36">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="61" t="s">
-        <v>264</v>
+        <v>63</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>263</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="61" t="s">
-        <v>302</v>
+        <v>113</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>311</v>
       </c>
       <c r="G34" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="36">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="61" t="s">
-        <v>265</v>
+        <v>64</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>264</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="61" t="s">
-        <v>312</v>
+        <v>114</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>302</v>
       </c>
       <c r="G35" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="61" t="s">
-        <v>266</v>
+        <v>65</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>265</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="F36" s="61" t="s">
-        <v>313</v>
+        <v>115</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>312</v>
       </c>
       <c r="G36" s="41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="36">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" s="61" t="s">
-        <v>267</v>
+        <v>66</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>266</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="F37" s="61" t="s">
-        <v>314</v>
+        <v>116</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>313</v>
       </c>
       <c r="G37" s="41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="36">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="61" t="s">
-        <v>268</v>
+        <v>67</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>267</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="61" t="s">
-        <v>315</v>
+        <v>117</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>314</v>
       </c>
       <c r="G38" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="36">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="61" t="s">
-        <v>269</v>
+        <v>68</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>268</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="F39" s="61" t="s">
-        <v>313</v>
+        <v>118</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>315</v>
       </c>
       <c r="G39" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="36">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="61" t="s">
-        <v>270</v>
+        <v>69</v>
+      </c>
+      <c r="C40" s="42" t="s">
+        <v>269</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="F40" s="61" t="s">
-        <v>316</v>
+        <v>119</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>313</v>
       </c>
       <c r="G40" s="41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="36">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="61" t="s">
-        <v>271</v>
+        <v>70</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>270</v>
       </c>
       <c r="D41" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="F41" s="61" t="s">
-        <v>317</v>
+        <v>120</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>316</v>
       </c>
       <c r="G41" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="36">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="61" t="s">
-        <v>272</v>
+        <v>71</v>
+      </c>
+      <c r="C42" s="42" t="s">
+        <v>271</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F42" s="61" t="s">
-        <v>318</v>
+        <v>121</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>317</v>
       </c>
       <c r="G42" s="41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="36">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43" s="61" t="s">
-        <v>273</v>
+        <v>72</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>272</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="F43" s="61" t="s">
-        <v>319</v>
+        <v>122</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>318</v>
       </c>
       <c r="G43" s="41" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="36">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" s="61" t="s">
-        <v>274</v>
+        <v>73</v>
+      </c>
+      <c r="C44" s="42" t="s">
+        <v>273</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="61" t="s">
-        <v>320</v>
+        <v>123</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>319</v>
       </c>
       <c r="G44" s="41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="36">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" s="61" t="s">
-        <v>275</v>
+        <v>74</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>274</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="61" t="s">
-        <v>321</v>
+        <v>124</v>
+      </c>
+      <c r="F45" s="42" t="s">
+        <v>320</v>
       </c>
       <c r="G45" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="36">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="61" t="s">
-        <v>276</v>
+        <v>75</v>
+      </c>
+      <c r="C46" s="42" t="s">
+        <v>275</v>
       </c>
       <c r="D46" s="41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="F46" s="61" t="s">
-        <v>322</v>
+        <v>125</v>
+      </c>
+      <c r="F46" s="42" t="s">
+        <v>321</v>
       </c>
       <c r="G46" s="41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="36">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" s="62">
-        <v>1150021595</v>
+        <v>76</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>276</v>
       </c>
       <c r="D47" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="61" t="s">
-        <v>323</v>
+        <v>126</v>
+      </c>
+      <c r="F47" s="42" t="s">
+        <v>322</v>
       </c>
       <c r="G47" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="36">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="61" t="s">
-        <v>277</v>
+        <v>77</v>
+      </c>
+      <c r="C48" s="43">
+        <v>1150021595</v>
       </c>
       <c r="D48" s="41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="61" t="s">
-        <v>324</v>
+        <v>127</v>
+      </c>
+      <c r="F48" s="42" t="s">
+        <v>323</v>
       </c>
       <c r="G48" s="41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="36">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" s="61" t="s">
-        <v>278</v>
+        <v>78</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>277</v>
       </c>
       <c r="D49" s="41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="F49" s="61" t="s">
-        <v>325</v>
+        <v>128</v>
+      </c>
+      <c r="F49" s="42" t="s">
+        <v>324</v>
       </c>
       <c r="G49" s="41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="36">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="61" t="s">
-        <v>279</v>
+        <v>79</v>
+      </c>
+      <c r="C50" s="42" t="s">
+        <v>278</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="F50" s="61" t="s">
-        <v>326</v>
+        <v>129</v>
+      </c>
+      <c r="F50" s="42" t="s">
+        <v>325</v>
       </c>
       <c r="G50" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="36">
+        <v>49</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="D51" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="F51" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="G51" s="41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A52" s="36">
         <v>50</v>
       </c>
-      <c r="B51" s="35" t="s">
+      <c r="B52" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="61" t="s">
+      <c r="C52" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="D51" s="41" t="s">
+      <c r="D52" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="E51" s="40" t="s">
+      <c r="E52" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="F51" s="61" t="s">
+      <c r="F52" s="42" t="s">
         <v>327</v>
       </c>
-      <c r="G51" s="41" t="s">
+      <c r="G52" s="41" t="s">
         <v>231</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>